--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128053067</v>
       </c>
       <c r="B2" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128053264</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128053067</v>
       </c>
       <c r="B2" t="n">
-        <v>58349</v>
+        <v>58350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128053264</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128053067</v>
       </c>
       <c r="B2" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Ellen Payne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,7 +792,7 @@
         <v>128053264</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Ellen Payne</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ellen Payne</t>
+          <t>Ellen Payne, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ellen Payne</t>
+          <t>Ellen Payne, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128053067</v>
       </c>
       <c r="B2" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128053264</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,832 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128811697</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552904</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706319</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128811718</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552922</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706284</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128811709</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552922</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706287</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128811729</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98509</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706290</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128811712</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552915</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128811702</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97463</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552868</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706345</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128811716</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552883</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128811710</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552916</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706287</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128811697</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,35 +1217,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B7" t="n">
-        <v>98509</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1255,7 +1264,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,44 +1323,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1217,44 +1217,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1264,7 +1255,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,35 +1314,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98536</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1217,44 +1217,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1264,7 +1255,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,35 +1314,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98568</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1217,35 +1217,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B7" t="n">
-        <v>98576</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1255,7 +1264,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,44 +1323,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128811697</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128811712</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>128811729</v>
       </c>
       <c r="B8" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,44 +1217,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1264,7 +1255,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,35 +1314,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98586</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128811697</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,35 +1217,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B7" t="n">
-        <v>98593</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1255,7 +1264,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,44 +1323,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1217,44 +1217,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1264,7 +1255,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,35 +1314,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98595</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,35 +1217,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B7" t="n">
-        <v>98595</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1255,7 +1264,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,44 +1323,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128811718</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128811709</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,44 +1217,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128811712</v>
+        <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1264,7 +1255,7 @@
         <v>552915</v>
       </c>
       <c r="R7" t="n">
-        <v>6706300</v>
+        <v>6706290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,35 +1314,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811729</v>
+        <v>128811712</v>
       </c>
       <c r="B8" t="n">
-        <v>98621</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
@@ -1361,7 +1361,7 @@
         <v>552915</v>
       </c>
       <c r="R8" t="n">
-        <v>6706290</v>
+        <v>6706300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>128811702</v>
       </c>
       <c r="B9" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>128811716</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128053067</v>
+        <v>128811695</v>
       </c>
       <c r="B2" t="n">
-        <v>58366</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högåsberget, Dlr</t>
+          <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553000</v>
+        <v>552943</v>
       </c>
       <c r="R2" t="n">
-        <v>6706407</v>
+        <v>6706270</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB/Ellen Payne</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,72 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128053264</v>
+        <v>109534980</v>
       </c>
       <c r="B3" t="n">
-        <v>58059</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högåsberget, Dlr</t>
+          <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552846</v>
+        <v>552876</v>
       </c>
       <c r="R3" t="n">
-        <v>6706443</v>
+        <v>6706292</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,17 +838,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB/Ellen Payne</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,50 +868,51 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128811697</v>
+        <v>109534893</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,13 +921,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552904</v>
+        <v>552849</v>
       </c>
       <c r="R4" t="n">
-        <v>6706319</v>
+        <v>6706352</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,42 +993,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128811718</v>
+        <v>128811697</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552922</v>
+        <v>552904</v>
       </c>
       <c r="R5" t="n">
-        <v>6706284</v>
+        <v>6706319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128811709</v>
+        <v>128811728</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552922</v>
+        <v>552865</v>
       </c>
       <c r="R6" t="n">
-        <v>6706287</v>
+        <v>6706332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1195,7 @@
         <v>128811729</v>
       </c>
       <c r="B7" t="n">
-        <v>98622</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128811712</v>
+        <v>109534586</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,7 +1319,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1352,19 +1327,20 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552915</v>
+        <v>552859</v>
       </c>
       <c r="R8" t="n">
-        <v>6706300</v>
+        <v>6706358</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,12 +1364,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,48 +1406,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128811702</v>
+        <v>109534844</v>
       </c>
       <c r="B9" t="n">
-        <v>97576</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552868</v>
+        <v>552849</v>
       </c>
       <c r="R9" t="n">
-        <v>6706345</v>
+        <v>6706352</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1485,12 +1472,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128811716</v>
+        <v>128811709</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1561,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552883</v>
+        <v>552922</v>
       </c>
       <c r="R10" t="n">
-        <v>6706298</v>
+        <v>6706287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1623,7 @@
         <v>128811710</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,6 +1723,1048 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128811712</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552915</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706300</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128811714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552869</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6706304</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128811715</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552852</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706311</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128811716</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552883</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6706298</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128811717</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552872</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706303</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128811718</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>552922</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706284</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128811722</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552840</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128811723</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>552869</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706299</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128811701</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>552865</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706332</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128811702</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Morkullberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>552868</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706345</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40765-2025 artfynd.xlsx
+++ b/artfynd/A 40765-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534893</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811697</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534586</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811709</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811710</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811714</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811715</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811716</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811717</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811718</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811722</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2571,6 +2661,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811723</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811701</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2765,8 +2865,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>